--- a/july 2026/LMT_JULY_26/July Orders/29-07-26/Zubaida Associates.xlsx
+++ b/july 2026/LMT_JULY_26/July Orders/29-07-26/Zubaida Associates.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30DC2233-5899-4B9A-A2D7-E0C1C42E7AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A2EB4A-E804-41A9-9AD9-60B5F3FC5FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -49,6 +49,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'3'!$A$1:$Q$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -7096,7 +7097,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -7124,7 +7125,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -8498,7 +8499,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -8526,7 +8527,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -9900,7 +9901,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -9928,7 +9929,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -11302,7 +11303,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -11330,7 +11331,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -12704,7 +12705,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -12732,7 +12733,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -14106,7 +14107,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -14134,7 +14135,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -15508,7 +15509,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -15536,7 +15537,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -16910,7 +16911,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -16938,7 +16939,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -18312,7 +18313,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -18340,7 +18341,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -19714,7 +19715,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -19742,7 +19743,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -23531,7 +23532,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -23559,7 +23560,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -24933,7 +24934,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -24961,7 +24962,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -26335,7 +26336,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -26363,7 +26364,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -27737,7 +27738,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -27765,7 +27766,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -29139,7 +29140,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -29167,7 +29168,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -30541,7 +30542,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -30569,7 +30570,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -31943,7 +31944,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -31971,7 +31972,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -33345,7 +33346,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -33373,7 +33374,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -34747,7 +34748,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -34775,7 +34776,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -36149,7 +36150,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -36177,7 +36178,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -40324,7 +40325,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -40352,7 +40353,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -41726,7 +41727,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -41754,7 +41755,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -43128,7 +43129,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -43156,7 +43157,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -44530,7 +44531,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -44558,7 +44559,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -45932,7 +45933,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -45960,7 +45961,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -47331,7 +47332,7 @@
       <c r="L4" s="384"/>
       <c r="M4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="N4" s="387"/>
       <c r="O4" s="387"/>
@@ -47359,7 +47360,7 @@
       <c r="L5" s="384"/>
       <c r="M5" s="387">
         <f ca="1">M4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="N5" s="383"/>
       <c r="O5" s="383"/>
@@ -53651,7 +53652,7 @@
       </c>
       <c r="T5" s="301">
         <f>+'3'!P35</f>
-        <v>0</v>
+        <v>123249.13997033896</v>
       </c>
       <c r="XEX5" t="s">
         <v>106</v>
@@ -53895,7 +53896,7 @@
       </c>
       <c r="G9" s="286">
         <f>+'1'!G18+'2'!G18+'3'!G18+'4'!G18+'5'!G18+'6'!G18+'7'!G18+'8'!G18+'9'!G18+'10'!G18+'11'!G18+'12'!G18+'13'!G18+'14'!G18+'15'!G18+'16'!G18+'17'!G18+'18'!G18+'19'!G18+'20'!G18+'21'!G18+'22'!G18+'23'!G18+'24'!G18+'25'!G18+'26'!G18+'27'!G18+'28'!G18+'29'!G18+'30'!G18</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H9" s="309">
         <f>+'1'!H18+'2'!H18+'3'!H18+'4'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18+'19'!H18+'20'!H18+'21'!H18+'22'!H18+'23'!H18+'24'!H18+'25'!H18+'26'!H18+'27'!H18+'28'!H18+'29'!H18+'30'!H18</f>
@@ -53903,15 +53904,15 @@
       </c>
       <c r="I9" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>125910</v>
       </c>
       <c r="J9" s="286">
         <f>+'1'!J18+'2'!J18+'3'!J18+'4'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18+'19'!J18+'20'!J18+'21'!J18+'22'!J18+'23'!J18+'24'!J18+'25'!J18+'26'!J18+'27'!J18+'28'!J18+'29'!J18+'30'!J18</f>
-        <v>0</v>
+        <v>22663.8</v>
       </c>
       <c r="K9" s="286">
         <f>+'1'!K18+'2'!K18+'3'!K18+'4'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18+'11'!K18+'12'!K18+'13'!K18+'14'!K18+'15'!K18+'16'!K18+'17'!K18+'18'!K18+'19'!K18+'20'!K18+'21'!K18+'22'!K18+'23'!K18+'24'!K18+'25'!K18+'26'!K18+'27'!K18+'28'!K18+'29'!K18+'30'!K18</f>
-        <v>0</v>
+        <v>4406.8500000000004</v>
       </c>
       <c r="L9" s="286">
         <f>+'1'!L18+'2'!L18+'3'!L18+'4'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18+'11'!L18+'12'!L18+'13'!L18+'14'!L18+'15'!L18+'16'!L18+'17'!L18+'18'!L18+'19'!L18+'20'!L18+'21'!L18+'22'!L18+'23'!L18+'24'!L18+'25'!L18+'26'!L18+'27'!L18+'28'!L18+'29'!L18+'30'!L18</f>
@@ -53919,19 +53920,19 @@
       </c>
       <c r="M9" s="230">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>98839.35</v>
       </c>
       <c r="N9" s="286">
         <f>+'1'!N18+'2'!N18+'3'!N18+'4'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18+'11'!N18+'12'!N18+'13'!N18+'14'!N18+'15'!N18+'16'!N18+'17'!N18+'18'!N18+'19'!N18+'20'!N18+'21'!N18+'22'!N18+'23'!N18+'24'!N18+'25'!N18+'26'!N18+'27'!N18+'28'!N18+'29'!N18+'30'!N18</f>
-        <v>0</v>
+        <v>23796.610169491516</v>
       </c>
       <c r="O9" s="286">
         <f>+'1'!O18+'2'!O18+'3'!O18+'4'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18+'11'!O18+'12'!O18+'13'!O18+'14'!O18+'15'!O18+'16'!O18+'17'!O18+'18'!O18+'19'!O18+'20'!O18+'21'!O18+'22'!O18+'23'!O18+'24'!O18+'25'!O18+'26'!O18+'27'!O18+'28'!O18+'29'!O18+'30'!O18</f>
-        <v>0</v>
+        <v>613.17980084745761</v>
       </c>
       <c r="P9" s="119">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>123249.13997033898</v>
       </c>
       <c r="R9" s="299">
         <v>7</v>
@@ -54415,7 +54416,7 @@
       <c r="F16" s="347"/>
       <c r="G16" s="117">
         <f t="shared" ref="G16:M16" si="3">SUM(G7:G15)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H16" s="113">
         <f t="shared" si="3"/>
@@ -54423,15 +54424,15 @@
       </c>
       <c r="I16" s="114">
         <f t="shared" si="3"/>
-        <v>1345455.5</v>
+        <v>1471365.5</v>
       </c>
       <c r="J16" s="274">
         <f>SUM(J7:J15)</f>
-        <v>242181.99</v>
+        <v>264845.78999999998</v>
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
-        <v>47090.942500000005</v>
+        <v>51497.792500000003</v>
       </c>
       <c r="L16" s="276">
         <f t="shared" si="3"/>
@@ -54439,19 +54440,19 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>1056182.5675000001</v>
+        <v>1155021.9175</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
-        <v>254288.1355932203</v>
+        <v>278084.74576271186</v>
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>6552.3535154661022</v>
+        <v>7165.5333163135601</v>
       </c>
       <c r="P16" s="234">
         <f>SUM(P7:P15)</f>
-        <v>1317023.0566086865</v>
+        <v>1440272.1965790254</v>
       </c>
       <c r="R16" s="299">
         <v>14</v>
@@ -54534,7 +54535,7 @@
       <c r="O19" s="358"/>
       <c r="P19" s="139">
         <f>I16</f>
-        <v>1345455.5</v>
+        <v>1471365.5</v>
       </c>
       <c r="R19" s="299">
         <v>17</v>
@@ -54566,7 +54567,7 @@
       <c r="O20" s="360"/>
       <c r="P20" s="140">
         <f>+J16</f>
-        <v>242181.99</v>
+        <v>264845.78999999998</v>
       </c>
       <c r="R20" s="299">
         <v>18</v>
@@ -54598,7 +54599,7 @@
       <c r="O21" s="360"/>
       <c r="P21" s="140">
         <f>+K16+L16</f>
-        <v>47090.942500000005</v>
+        <v>51497.792500000003</v>
       </c>
       <c r="R21" s="299">
         <v>19</v>
@@ -54631,7 +54632,7 @@
       <c r="O22" s="360"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>1056182.5674999999</v>
+        <v>1155021.9175</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -54666,7 +54667,7 @@
       </c>
       <c r="P23" s="140">
         <f>+N16</f>
-        <v>254288.1355932203</v>
+        <v>278084.74576271186</v>
       </c>
       <c r="R23" s="299">
         <v>21</v>
@@ -54699,7 +54700,7 @@
       <c r="O24" s="362"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>1310470.7030932202</v>
+        <v>1433106.6632627118</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -54735,7 +54736,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>6552.3535154661022</v>
+        <v>7165.5333163135601</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -54756,7 +54757,7 @@
       <c r="O26" s="364"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>1317023.0566086865</v>
+        <v>1440272.1965790254</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -54870,7 +54871,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>1317023.0566086862</v>
+        <v>1440272.1965790251</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -56422,7 +56423,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -56450,7 +56451,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -57763,6 +57764,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:XFD38"/>
   <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -57773,14 +57777,14 @@
     <col min="6" max="6" width="6.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.453125" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" customWidth="1"/>
-    <col min="10" max="10" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="9.1796875" style="61" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.54296875" customWidth="1"/>
-    <col min="16" max="16" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.36328125" style="61" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="19" max="21" width="6.1796875" style="61" customWidth="1"/>
@@ -57833,7 +57837,6 @@
       <c r="L4" s="384"/>
       <c r="M4" s="384"/>
       <c r="N4" s="387">
-        <f ca="1">TODAY()+1</f>
         <v>46234</v>
       </c>
       <c r="O4" s="387"/>
@@ -57861,7 +57864,7 @@
       <c r="L5" s="384"/>
       <c r="M5" s="384"/>
       <c r="N5" s="387">
-        <f ca="1">N4-1</f>
+        <f>N4-1</f>
         <v>46233</v>
       </c>
       <c r="O5" s="383"/>
@@ -57883,7 +57886,7 @@
       <c r="L6" s="384"/>
       <c r="M6" s="384"/>
       <c r="N6" s="386" t="s">
-        <v>62</v>
+        <v>501</v>
       </c>
       <c r="O6" s="386"/>
       <c r="P6" s="386"/>
@@ -58028,7 +58031,7 @@
         <v>481</v>
       </c>
       <c r="B12" s="241" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" s="81" t="str">
         <f>IF($O32&gt;21.99%,"No","Yes")</f>
@@ -58101,7 +58104,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:22 16383:16384" ht="20.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:22 16383:16384" ht="30.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="336"/>
       <c r="B15" s="337"/>
       <c r="C15" s="339"/>
@@ -58328,19 +58331,21 @@
         <f>VLOOKUP(A18,'Cust. Price List'!D8:M16,10,0)</f>
         <v>52.462499999999999</v>
       </c>
-      <c r="G18" s="287"/>
+      <c r="G18" s="287">
+        <v>60</v>
+      </c>
       <c r="H18" s="96"/>
       <c r="I18" s="236">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>125910</v>
       </c>
       <c r="J18" s="272">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22663.8</v>
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4406.8500000000004</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -58348,19 +58353,19 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>98839.35</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>23796.610169491516</v>
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>613.17980084745761</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>123249.13997033898</v>
       </c>
       <c r="S18" s="269">
         <f>+S17</f>
@@ -58829,7 +58834,7 @@
       <c r="F25" s="347"/>
       <c r="G25" s="117">
         <f t="shared" ref="G25:M25" si="7">SUM(G16:G24)</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H25" s="113">
         <f t="shared" si="7"/>
@@ -58837,15 +58842,15 @@
       </c>
       <c r="I25" s="114">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>125910</v>
       </c>
       <c r="J25" s="274">
         <f>SUM(J16:J24)</f>
-        <v>0</v>
+        <v>22663.8</v>
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4406.8500000000004</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -58853,19 +58858,19 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>98839.35</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
-        <v>0</v>
+        <v>23796.610169491516</v>
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>0</v>
+        <v>613.17980084745761</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>0</v>
+        <v>123249.13997033898</v>
       </c>
     </row>
     <row r="26" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
@@ -58915,7 +58920,7 @@
       <c r="O28" s="358"/>
       <c r="P28" s="139">
         <f>I25</f>
-        <v>0</v>
+        <v>125910</v>
       </c>
     </row>
     <row r="29" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58936,7 +58941,7 @@
       <c r="O29" s="360"/>
       <c r="P29" s="140">
         <f>+J25</f>
-        <v>0</v>
+        <v>22663.8</v>
       </c>
     </row>
     <row r="30" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58957,7 +58962,7 @@
       <c r="O30" s="360"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>0</v>
+        <v>4406.8500000000004</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -58979,7 +58984,7 @@
       <c r="O31" s="360"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>0</v>
+        <v>98839.349999999991</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59003,7 +59008,7 @@
       </c>
       <c r="P32" s="140">
         <f>+N25</f>
-        <v>0</v>
+        <v>23796.610169491516</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -59025,7 +59030,7 @@
       <c r="O33" s="362"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>0</v>
+        <v>122635.9601694915</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -59050,7 +59055,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>0</v>
+        <v>613.1798008474575</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -59060,7 +59065,7 @@
       <c r="O35" s="364"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>0</v>
+        <v>123249.13997033896</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -59135,7 +59140,7 @@
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="N4:P4"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>$XFC$3:$XFC$4</formula1>
     </dataValidation>
@@ -59147,10 +59152,10 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="85" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0600-000003000000}">
           <x14:formula1>
             <xm:f>Summary!$B$44:$B$48</xm:f>
@@ -59236,7 +59241,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -59264,7 +59269,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -60638,7 +60643,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -60666,7 +60671,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
